--- a/testdata/datafortesting.xlsx
+++ b/testdata/datafortesting.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -521,7 +521,7 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>301</v>
+        <v>396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         <v>391</v>
       </c>
       <c r="C10" t="n">
-        <v>295</v>
+        <v>358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/testdata/datafortesting.xlsx
+++ b/testdata/datafortesting.xlsx
@@ -467,11 +467,11 @@
         <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
     </row>
@@ -485,11 +485,11 @@
         <v>82</v>
       </c>
       <c r="C3" t="n">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
         <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
